--- a/Group03_23130094_BuiAnhHau.xlsx
+++ b/Group03_23130094_BuiAnhHau.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="274">
   <si>
     <t xml:space="preserve">TEST CASE</t>
   </si>
@@ -589,9 +589,6 @@
   </si>
   <si>
     <t xml:space="preserve">1. New contract screen is displayed (page title = "New contract")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã chạy thực tế ngày 20-Oct-2026</t>
   </si>
   <si>
     <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists.
@@ -608,9 +605,6 @@
     - Buttons [CREATE DRAFT] and [CANCEL]</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã chạy thực tế ngày 20-Oct-2026. Demo còn có trường "aaa" (Automatically calculated) - trường tùy chỉnh, không kiểm tra</t>
-  </si>
-  <si>
     <t xml:space="preserve">Check creating a draft contract with only the required field (Third party)</t>
   </si>
   <si>
@@ -624,9 +618,6 @@
     - Status = Draft
     - Ref is a provisional ref (e.g. "(PROV...)")
     - Third party = Testldr1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã chạy thực tế ngày 20-Oct-2026: tạo được hợp đồng (PROV24), Status Draft, Third party Testldr1</t>
   </si>
   <si>
     <t xml:space="preserve">Check creating a contract with Note (internal) filled</t>
@@ -643,9 +634,6 @@
 4. Tab [Notes] shows the internal note = "Internal note 01"</t>
   </si>
   <si>
-    <t xml:space="preserve">Ô Note (public) là trình soạn thảo rich text, khó record nên chỉ nhập Note (internal)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Check required field - Third party</t>
   </si>
   <si>
@@ -657,9 +645,6 @@
     <t xml:space="preserve">2. New contract screen is still displayed
     - Error message "Field 'Third party' is required" is displayed
     - No contract is created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã chạy thực tế ngày 20-Oct-2026: thông báo lỗi đỏ hiện ở góc trên bên phải</t>
   </si>
   <si>
     <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. Third party = Testldr1.
@@ -718,9 +703,6 @@
     - Contract date = 01/01/2026 is displayed on Contract detail screen</t>
   </si>
   <si>
-    <t xml:space="preserve">Ngày hiển thị theo định dạng MM/DD/YYYY của bản demo</t>
-  </si>
-  <si>
     <t xml:space="preserve">ADD_CONTRACT-10</t>
   </si>
   <si>
@@ -748,9 +730,6 @@
     - Contract is created and Contract detail screen is displayed</t>
   </si>
   <si>
-    <t xml:space="preserve">Kiểm tra khả năng chịu dữ liệu dài; ghi lại hành vi thực tế (có cắt ký tự hay không)</t>
-  </si>
-  <si>
     <t xml:space="preserve">LIST_CONTRACT</t>
   </si>
   <si>
@@ -768,9 +747,6 @@
     - Table of contracts is displayed</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã chạy thực tế ngày 20-Oct-2026: Passed</t>
-  </si>
-  <si>
     <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists.
 1. Open Contracts list screen (LIST_CONTRACT-01)
 2. Check the columns, the filter row and the icons</t>
@@ -782,9 +758,6 @@
     - Rows of contracts below</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã chạy thực tế ngày 20-Oct-2026. Demo có thêm cột "aaa" (trường tùy chỉnh của bản demo, hiển thị lỗi) - không đưa vào Expected</t>
-  </si>
-  <si>
     <t xml:space="preserve">Check searching contracts by an existing Ref</t>
   </si>
   <si>
@@ -833,9 +806,6 @@
     <t xml:space="preserve">3. All displayed contracts have Status = Draft</t>
   </si>
   <si>
-    <t xml:space="preserve">Ô Status nằm bên phải bảng; nếu khó thao tác/record thì đánh dấu Skipped</t>
-  </si>
-  <si>
     <t xml:space="preserve">Check clearing the filter</t>
   </si>
   <si>
@@ -883,9 +853,6 @@
     - Third party is the same as in the list</t>
   </si>
   <si>
-    <t xml:space="preserve">Demo dùng chung có thể reset; nếu không còn CT2610-0007 thì chọn contract đầu tiên trong danh sách</t>
-  </si>
-  <si>
     <t xml:space="preserve">Check going back to the list from Contract detail screen</t>
   </si>
   <si>
@@ -894,9 +861,6 @@
   </si>
   <si>
     <t xml:space="preserve">1. Contracts list screen is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã chạy thực tế ngày 20-Oct-2026: link Back to list ở góc trên bên phải trang chi tiết</t>
   </si>
   <si>
     <t xml:space="preserve">EDIT_CONTRACT</t>
@@ -916,9 +880,6 @@
 4. Ref. customer = RC_EDIT_01 is displayed on Contract detail screen</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã chạy thực tế ngày 20-Oct-2026: sửa Ref. customer thành RC_EDIT_01 bằng biểu tượng bút chì</t>
-  </si>
-  <si>
     <t xml:space="preserve">Check cancelling modify Ref. customer</t>
   </si>
   <si>
@@ -949,9 +910,6 @@
     <t xml:space="preserve">2. A confirmation message is displayed
 3. Back to Contracts list screen
 4. The deleted contract is not displayed in the list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã chạy thực tế ngày 20-Oct-2026. Chỉ xóa hợp đồng nháp do mình tạo (demo dùng chung)</t>
   </si>
   <si>
     <t xml:space="preserve">Check cancelling delete contract</t>
@@ -2707,7 +2665,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="n">
         <f aca="false">COUNTIF(F9:F996,"Passed")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">COUNTIF(F9:F996,"Failed")</f>
@@ -2715,7 +2673,7 @@
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">F6-E6-D6-B6-A6</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" s="22" t="n">
         <f aca="false">COUNTIF(F9:F996,"Blocked")</f>
@@ -2775,15 +2733,9 @@
       <c r="E9" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>187</v>
-      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
@@ -2793,97 +2745,77 @@
         <v>57</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>189</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>190</v>
-      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>191</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>193</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>194</v>
-      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="121.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>55</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="23"/>
-      <c r="H12" s="9" t="s">
-        <v>198</v>
-      </c>
+      <c r="H12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>68</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G13" s="23" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>202</v>
-      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
@@ -2893,10 +2825,10 @@
         <v>70</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>62</v>
@@ -2910,13 +2842,13 @@
         <v>74</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>89</v>
@@ -2930,13 +2862,13 @@
         <v>77</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>62</v>
@@ -2947,38 +2879,36 @@
     </row>
     <row r="17" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>55</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="23"/>
-      <c r="H17" s="9" t="s">
-        <v>215</v>
-      </c>
+      <c r="H17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>82</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>55</v>
@@ -2989,25 +2919,23 @@
     </row>
     <row r="19" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>55</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="23"/>
-      <c r="H19" s="9" t="s">
-        <v>222</v>
-      </c>
+      <c r="H19" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F9:F996">
@@ -3061,7 +2989,7 @@
         <v>167</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="J2" s="21" t="s">
         <v>169</v>
@@ -3115,7 +3043,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="n">
         <f aca="false">COUNTIF(F9:F996,"Passed")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">COUNTIF(F9:F996,"Failed")</f>
@@ -3123,7 +3051,7 @@
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">F6-E6-D6-B6-A6</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D6" s="22" t="n">
         <f aca="false">COUNTIF(F9:F996,"Blocked")</f>
@@ -3172,24 +3100,18 @@
         <v>89</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>227</v>
-      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
@@ -3199,88 +3121,70 @@
         <v>91</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>230</v>
-      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
         <v>95</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>187</v>
-      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
         <v>98</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G12" s="23" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>187</v>
-      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>101</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>89</v>
@@ -3294,61 +3198,53 @@
         <v>104</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>89</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="23"/>
-      <c r="H14" s="9" t="s">
-        <v>243</v>
-      </c>
+      <c r="H14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
         <v>107</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G15" s="23" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>187</v>
-      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
         <v>110</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>89</v>
@@ -3362,13 +3258,13 @@
         <v>112</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>89</v>
@@ -3382,48 +3278,40 @@
         <v>115</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>89</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="23"/>
-      <c r="H18" s="9" t="s">
-        <v>256</v>
-      </c>
+      <c r="H18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G19" s="23" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>260</v>
-      </c>
+      <c r="F19" s="8"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F9:F996">
@@ -3477,7 +3365,7 @@
         <v>167</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="J2" s="21" t="s">
         <v>169</v>
@@ -3531,7 +3419,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="n">
         <f aca="false">COUNTIF(F9:F996,"Passed")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">COUNTIF(F9:F996,"Failed")</f>
@@ -3539,7 +3427,7 @@
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">F6-E6-D6-B6-A6</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="22" t="n">
         <f aca="false">COUNTIF(F9:F996,"Blocked")</f>
@@ -3588,39 +3476,33 @@
         <v>122</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>265</v>
-      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="121.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
         <v>125</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>62</v>
@@ -3681,7 +3563,7 @@
         <v>167</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="J2" s="21" t="s">
         <v>169</v>
@@ -3735,7 +3617,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="n">
         <f aca="false">COUNTIF(F9:F996,"Passed")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">COUNTIF(F9:F996,"Failed")</f>
@@ -3743,7 +3625,7 @@
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">F6-E6-D6-B6-A6</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="22" t="n">
         <f aca="false">COUNTIF(F9:F996,"Blocked")</f>
@@ -3792,39 +3674,33 @@
         <v>129</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>273</v>
-      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
         <v>132</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>62</v>
@@ -3878,7 +3754,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="11" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3913,7 +3789,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>9</v>
@@ -3924,7 +3800,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="2" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3932,13 +3808,13 @@
         <v>27</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>174</v>
@@ -3950,7 +3826,7 @@
         <v>175</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3963,7 +3839,7 @@
       </c>
       <c r="D11" s="8" t="n">
         <f aca="false">'Add Contract'!A6</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
         <f aca="false">'Add Contract'!B6</f>
@@ -3971,7 +3847,7 @@
       </c>
       <c r="F11" s="8" t="n">
         <f aca="false">'Add Contract'!C6</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G11" s="8" t="n">
         <f aca="false">'Add Contract'!D6</f>
@@ -3996,7 +3872,7 @@
       </c>
       <c r="D12" s="8" t="n">
         <f aca="false">'List Contract'!A6</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E12" s="8" t="n">
         <f aca="false">'List Contract'!B6</f>
@@ -4004,7 +3880,7 @@
       </c>
       <c r="F12" s="8" t="n">
         <f aca="false">'List Contract'!C6</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G12" s="8" t="n">
         <f aca="false">'List Contract'!D6</f>
@@ -4029,7 +3905,7 @@
       </c>
       <c r="D13" s="8" t="n">
         <f aca="false">'Edit Contract'!A6</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="8" t="n">
         <f aca="false">'Edit Contract'!B6</f>
@@ -4037,7 +3913,7 @@
       </c>
       <c r="F13" s="8" t="n">
         <f aca="false">'Edit Contract'!C6</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="8" t="n">
         <f aca="false">'Edit Contract'!D6</f>
@@ -4062,7 +3938,7 @@
       </c>
       <c r="D14" s="8" t="n">
         <f aca="false">'Delete Contract'!A6</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="8" t="n">
         <f aca="false">'Delete Contract'!B6</f>
@@ -4070,7 +3946,7 @@
       </c>
       <c r="F14" s="8" t="n">
         <f aca="false">'Delete Contract'!C6</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="8" t="n">
         <f aca="false">'Delete Contract'!D6</f>
@@ -4087,11 +3963,11 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="7" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="D15" s="7" t="n">
         <f aca="false">SUM(D11:D14)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
         <f aca="false">SUM(E11:E14)</f>
@@ -4099,7 +3975,7 @@
       </c>
       <c r="F15" s="7" t="n">
         <f aca="false">SUM(F11:F14)</f>
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G15" s="7" t="n">
         <f aca="false">SUM(G11:G14)</f>
@@ -4116,26 +3992,26 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="2" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="E17" s="24" t="n">
         <f aca="false">IFERROR((D15+E15)*100/(I15-G15-H15),0)</f>
-        <v>46.1538461538462</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="2" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="E18" s="24" t="n">
         <f aca="false">IFERROR(D15*100/(D15+E15),0)</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/Group03_23130094_BuiAnhHau.xlsx
+++ b/Group03_23130094_BuiAnhHau.xlsx
@@ -11,11 +11,8 @@
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Test case List" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="TestDesign" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Add Contract" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="List Contract" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Edit Contract" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Delete Contract" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Test Report" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Contracts" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Test Report" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="261">
   <si>
     <t xml:space="preserve">TEST CASE</t>
   </si>
@@ -125,40 +122,10 @@
     <t xml:space="preserve">Pre-Condition</t>
   </si>
   <si>
-    <t xml:space="preserve">Add Contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a contract (draft) and validate the required field and field values.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sign in and access Contracts; at least 1 Third party exists.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List / Search Contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List Contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List, search, filter, sort and view contracts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sign in; the contract list has sample data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edit Contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Update data of a draft contract and verify the change.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sign in and prepare a draft contract owned by the tester.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delete Contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check deletion and cancel behavior using tester-owned draft contracts.</t>
+    <t xml:space="preserve">Create, list/search/sort, view, edit and delete (draft) contracts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign in; at least 1 Third party exists; the contract list has sample data.</t>
   </si>
   <si>
     <t xml:space="preserve">Requirement Level 1</t>
@@ -194,7 +161,7 @@
     <t xml:space="preserve">Function</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT-01</t>
+    <t xml:space="preserve">CONTRACT_Create_01</t>
   </si>
   <si>
     <t xml:space="preserve">Screen / Layout and defaults</t>
@@ -206,7 +173,7 @@
     <t xml:space="preserve">GUI</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT-02</t>
+    <t xml:space="preserve">CONTRACT_Create_02</t>
   </si>
   <si>
     <t xml:space="preserve">Successful create / Minimum data</t>
@@ -215,7 +182,7 @@
     <t xml:space="preserve">Check create a draft contract with only the required field (Third party)</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT-03</t>
+    <t xml:space="preserve">CONTRACT_Create_03</t>
   </si>
   <si>
     <t xml:space="preserve">Successful create / Note (internal)</t>
@@ -224,7 +191,7 @@
     <t xml:space="preserve">Check create a contract with Note (internal) filled</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT-04</t>
+    <t xml:space="preserve">CONTRACT_Create_04</t>
   </si>
   <si>
     <t xml:space="preserve">Required field / Third party</t>
@@ -233,7 +200,7 @@
     <t xml:space="preserve">Check reject creation when Third party is empty</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT-05</t>
+    <t xml:space="preserve">CONTRACT_Create_05</t>
   </si>
   <si>
     <t xml:space="preserve">Result in list</t>
@@ -242,7 +209,7 @@
     <t xml:space="preserve">Check new contract is displayed in the Contracts list after creating</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT-06</t>
+    <t xml:space="preserve">CONTRACT_Create_06</t>
   </si>
   <si>
     <t xml:space="preserve">Cancel creation</t>
@@ -251,7 +218,7 @@
     <t xml:space="preserve">Check cancel a New contract form without saving</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT-07</t>
+    <t xml:space="preserve">CONTRACT_Create_07</t>
   </si>
   <si>
     <t xml:space="preserve">Create continuously</t>
@@ -260,7 +227,7 @@
     <t xml:space="preserve">Check create two contracts continuously</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT-08</t>
+    <t xml:space="preserve">CONTRACT_Create_08</t>
   </si>
   <si>
     <t xml:space="preserve">Field value / Date</t>
@@ -269,7 +236,7 @@
     <t xml:space="preserve">Check create a contract with a past Date</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT-09; EP</t>
+    <t xml:space="preserve">CONTRACT_Create_09; EP</t>
   </si>
   <si>
     <t xml:space="preserve">Field value / Note (internal)</t>
@@ -278,13 +245,13 @@
     <t xml:space="preserve">Check Note (internal) with special characters</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT-10; EP</t>
+    <t xml:space="preserve">CONTRACT_Create_10; EP</t>
   </si>
   <si>
     <t xml:space="preserve">Check Note (internal) with a very long value (1000 characters)</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT-11; BVA</t>
+    <t xml:space="preserve">CONTRACT_Create_11; BVA</t>
   </si>
   <si>
     <t xml:space="preserve">1.2 Read</t>
@@ -296,7 +263,7 @@
     <t xml:space="preserve">Check open Contracts list via menu and verify the page title and table</t>
   </si>
   <si>
-    <t xml:space="preserve">LIST_CONTRACT-01</t>
+    <t xml:space="preserve">CONTRACT_List_01</t>
   </si>
   <si>
     <t xml:space="preserve">List layout</t>
@@ -305,7 +272,7 @@
     <t xml:space="preserve">Check layout of Contracts list screen</t>
   </si>
   <si>
-    <t xml:space="preserve">LIST_CONTRACT-02</t>
+    <t xml:space="preserve">CONTRACT_List_02</t>
   </si>
   <si>
     <t xml:space="preserve">Search by Ref.</t>
@@ -314,7 +281,7 @@
     <t xml:space="preserve">Check find a contract using an existing Ref.</t>
   </si>
   <si>
-    <t xml:space="preserve">LIST_CONTRACT-03</t>
+    <t xml:space="preserve">CONTRACT_Search_01</t>
   </si>
   <si>
     <t xml:space="preserve">Search / No match</t>
@@ -323,7 +290,7 @@
     <t xml:space="preserve">Check return no record for a non-existent Ref.</t>
   </si>
   <si>
-    <t xml:space="preserve">LIST_CONTRACT-04</t>
+    <t xml:space="preserve">CONTRACT_Search_02</t>
   </si>
   <si>
     <t xml:space="preserve">Search by Third party</t>
@@ -332,7 +299,7 @@
     <t xml:space="preserve">Check filter contracts by Third party</t>
   </si>
   <si>
-    <t xml:space="preserve">LIST_CONTRACT-05</t>
+    <t xml:space="preserve">CONTRACT_Search_03</t>
   </si>
   <si>
     <t xml:space="preserve">Filter by Status</t>
@@ -341,7 +308,7 @@
     <t xml:space="preserve">Check filter contracts by Status = Draft</t>
   </si>
   <si>
-    <t xml:space="preserve">LIST_CONTRACT-06</t>
+    <t xml:space="preserve">CONTRACT_Search_04</t>
   </si>
   <si>
     <t xml:space="preserve">Clear filter</t>
@@ -350,7 +317,7 @@
     <t xml:space="preserve">Check clear the applied filter</t>
   </si>
   <si>
-    <t xml:space="preserve">LIST_CONTRACT-07</t>
+    <t xml:space="preserve">CONTRACT_Search_05</t>
   </si>
   <si>
     <t xml:space="preserve">Sorting</t>
@@ -359,13 +326,13 @@
     <t xml:space="preserve">Check change sort by Ref. (ascending, descending)</t>
   </si>
   <si>
-    <t xml:space="preserve">LIST_CONTRACT-08</t>
+    <t xml:space="preserve">CONTRACT_Search_06</t>
   </si>
   <si>
     <t xml:space="preserve">Check change sort by Contract date (ascending, descending)</t>
   </si>
   <si>
-    <t xml:space="preserve">LIST_CONTRACT-09</t>
+    <t xml:space="preserve">CONTRACT_Search_07</t>
   </si>
   <si>
     <t xml:space="preserve">Details</t>
@@ -374,7 +341,7 @@
     <t xml:space="preserve">Check view Contract detail screen from the list</t>
   </si>
   <si>
-    <t xml:space="preserve">LIST_CONTRACT-10</t>
+    <t xml:space="preserve">CONTRACT_View_01</t>
   </si>
   <si>
     <t xml:space="preserve">Navigation</t>
@@ -383,7 +350,7 @@
     <t xml:space="preserve">Check go back to the list from Contract detail screen</t>
   </si>
   <si>
-    <t xml:space="preserve">LIST_CONTRACT-11</t>
+    <t xml:space="preserve">CONTRACT_View_02</t>
   </si>
   <si>
     <t xml:space="preserve">1.3 Update</t>
@@ -395,7 +362,7 @@
     <t xml:space="preserve">Check modify Ref. customer of a draft contract</t>
   </si>
   <si>
-    <t xml:space="preserve">EDIT_CONTRACT-01</t>
+    <t xml:space="preserve">CONTRACT_Edit_01</t>
   </si>
   <si>
     <t xml:space="preserve">Cancel edit</t>
@@ -404,7 +371,7 @@
     <t xml:space="preserve">Check cancel modify Ref. customer</t>
   </si>
   <si>
-    <t xml:space="preserve">EDIT_CONTRACT-02</t>
+    <t xml:space="preserve">CONTRACT_Edit_02</t>
   </si>
   <si>
     <t xml:space="preserve">1.4 Delete</t>
@@ -416,7 +383,7 @@
     <t xml:space="preserve">Check delete a draft contract and confirm</t>
   </si>
   <si>
-    <t xml:space="preserve">DELETE_CONTRACT-01</t>
+    <t xml:space="preserve">CONTRACT_Delete_01</t>
   </si>
   <si>
     <t xml:space="preserve">Cancel deletion</t>
@@ -425,7 +392,7 @@
     <t xml:space="preserve">Check cancel delete contract and the contract is preserved</t>
   </si>
   <si>
-    <t xml:space="preserve">DELETE_CONTRACT-02</t>
+    <t xml:space="preserve">CONTRACT_Delete_02</t>
   </si>
   <si>
     <t xml:space="preserve">2. Purchase Orders</t>
@@ -533,7 +500,7 @@
     <t xml:space="preserve">Module Code</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT</t>
+    <t xml:space="preserve">CONTRACT</t>
   </si>
   <si>
     <t xml:space="preserve">Passed</t>
@@ -592,7 +559,7 @@
   </si>
   <si>
     <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists.
-1. Open New contract screen (ADD_CONTRACT-01)
+1. Open New contract screen (CONTRACT_Create_01)
 2. Check the displayed fields, default values and buttons</t>
   </si>
   <si>
@@ -648,7 +615,7 @@
   </si>
   <si>
     <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. Third party = Testldr1.
-1. Create a draft contract (steps of ADD_CONTRACT-03)
+1. Create a draft contract (steps of CONTRACT_Create_03)
 2. Write down the Ref of the new contract on Contract detail screen
 3. Open Contracts list screen
 4. Input the Ref into the Ref. filter box and press Enter</t>
@@ -678,7 +645,7 @@
   <si>
     <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. Third party = Testldr1 (both contracts).
 1. Open Contracts list screen and write down n in the title "Contracts (n)"
-2. Create the 1st draft contract (steps of ADD_CONTRACT-03)
+2. Create the 1st draft contract (steps of CONTRACT_Create_03)
 3. Click [New contract or subscription] again and create the 2nd draft contract
 4. Open Contracts list screen</t>
   </si>
@@ -687,7 +654,7 @@
 4. Page title = "Contracts (n+2)"</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT-09</t>
+    <t xml:space="preserve">CONTRACT_Create_09</t>
   </si>
   <si>
     <t xml:space="preserve">Check creating a contract with a past Date</t>
@@ -703,7 +670,7 @@
     - Contract date = 01/01/2026 is displayed on Contract detail screen</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT-10</t>
+    <t xml:space="preserve">CONTRACT_Create_10</t>
   </si>
   <si>
     <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. Third party = Testldr1; Note (internal) = Note @#$%&amp;*().
@@ -717,7 +684,7 @@
 4. Tab [Notes] shows the internal note exactly as input: Note @#$%&amp;*()</t>
   </si>
   <si>
-    <t xml:space="preserve">ADD_CONTRACT-11</t>
+    <t xml:space="preserve">CONTRACT_Create_11</t>
   </si>
   <si>
     <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. Third party = Testldr1; Note (internal) = 1000 characters "A".
@@ -730,9 +697,6 @@
     - Contract is created and Contract detail screen is displayed</t>
   </si>
   <si>
-    <t xml:space="preserve">LIST_CONTRACT</t>
-  </si>
-  <si>
     <t xml:space="preserve">Check displaying Contracts list screen by selecting [Commercial] &gt; [Contracts/Subscriptions] &gt; [List] from the menu</t>
   </si>
   <si>
@@ -748,7 +712,7 @@
   </si>
   <si>
     <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists.
-1. Open Contracts list screen (LIST_CONTRACT-01)
+1. Open Contracts list screen (CONTRACT_List_01)
 2. Check the columns, the filter row and the icons</t>
   </si>
   <si>
@@ -809,7 +773,7 @@
     <t xml:space="preserve">Check clearing the filter</t>
   </si>
   <si>
-    <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. A filter is applied (e.g. LIST_CONTRACT-04).
+    <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. A filter is applied (e.g. CONTRACT_Search_02).
 1. On Contracts list screen with a filter applied, click the clear icon (X) in the filter row</t>
   </si>
   <si>
@@ -863,13 +827,10 @@
     <t xml:space="preserve">1. Contracts list screen is displayed</t>
   </si>
   <si>
-    <t xml:space="preserve">EDIT_CONTRACT</t>
-  </si>
-  <si>
     <t xml:space="preserve">Check modifying Ref. customer of a draft contract</t>
   </si>
   <si>
-    <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. A Draft contract exists (created in ADD_CONTRACT-03); new Ref. customer = RC_EDIT_01.
+    <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. A Draft contract exists (created in CONTRACT_Create_03); new Ref. customer = RC_EDIT_01.
 1. Open Contract detail screen of the draft contract
 2. Click the edit (pencil) icon next to [Ref. customer]
 3. Input Ref. customer = RC_EDIT_01
@@ -883,7 +844,7 @@
     <t xml:space="preserve">Check cancelling modify Ref. customer</t>
   </si>
   <si>
-    <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. A Draft contract exists (created in ADD_CONTRACT-03).
+    <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. A Draft contract exists (created in CONTRACT_Create_03).
 1. Open Contract detail screen of the draft contract
 2. Click the edit (pencil) icon next to [Ref. customer]
 3. Input Ref. customer = RC_NOEDIT_01
@@ -894,13 +855,10 @@
     - Ref. customer is NOT changed (not RC_NOEDIT_01)</t>
   </si>
   <si>
-    <t xml:space="preserve">DELETE_CONTRACT</t>
-  </si>
-  <si>
     <t xml:space="preserve">Check deleting a draft contract and confirming</t>
   </si>
   <si>
-    <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. A Draft contract exists (created in ADD_CONTRACT-03).
+    <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. A Draft contract exists (created in CONTRACT_Create_03).
 1. Open Contract detail screen of the draft contract
 2. Click [DELETE] button
 3. Confirm deleting on the confirmation message
@@ -915,7 +873,7 @@
     <t xml:space="preserve">Check cancelling delete contract</t>
   </si>
   <si>
-    <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. A Draft contract exists (created in ADD_CONTRACT-03).
+    <t xml:space="preserve">PRE: Signed in the Dolibarr demo with the Contracts module enabled; at least 1 Third party exists. A Draft contract exists (created in CONTRACT_Create_03).
 1. Open Contract detail screen of the draft contract
 2. Click [DELETE] button
 3. Click [No] (or close) on the confirmation message</t>
@@ -1657,7 +1615,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:F12"/>
+  <dimension ref="B1:F9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1723,67 +1681,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1792,10 +1699,7 @@
     <mergeCell ref="D5:F5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D9" r:id="rId1" location="'Add%20Contract'!A1" display="Add Contract"/>
-    <hyperlink ref="D10" r:id="rId2" location="'List%20Contract'!A1" display="List Contract"/>
-    <hyperlink ref="D11" r:id="rId3" location="'Edit%20Contract'!A1" display="Edit Contract"/>
-    <hyperlink ref="D12" r:id="rId4" location="'Delete%20Contract'!A1" display="Delete Contract"/>
+    <hyperlink ref="D9" r:id="rId1" location="'Contracts'!A1" display="Contracts"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1824,481 +1728,481 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19"/>
       <c r="B3" s="19"/>
       <c r="C3" s="19" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19"/>
       <c r="B4" s="19"/>
       <c r="C4" s="19" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="19"/>
       <c r="B5" s="19"/>
       <c r="C5" s="19" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="19"/>
       <c r="B6" s="19"/>
       <c r="C6" s="19" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19"/>
       <c r="B7" s="19"/>
       <c r="C7" s="19" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19"/>
       <c r="B8" s="19"/>
       <c r="C8" s="19" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19"/>
       <c r="B9" s="19"/>
       <c r="C9" s="19" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19"/>
       <c r="B10" s="19"/>
       <c r="C10" s="19" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19"/>
       <c r="B11" s="19"/>
       <c r="C11" s="19" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19"/>
       <c r="B13" s="19" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19"/>
       <c r="B14" s="19"/>
       <c r="C14" s="19" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19"/>
       <c r="B15" s="19"/>
       <c r="C15" s="19" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="19"/>
       <c r="B16" s="19"/>
       <c r="C16" s="19" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19"/>
       <c r="B17" s="19"/>
       <c r="C17" s="19" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="19"/>
       <c r="B18" s="19"/>
       <c r="C18" s="19" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="19"/>
       <c r="B19" s="19"/>
       <c r="C19" s="19" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="19"/>
       <c r="B20" s="19"/>
       <c r="C20" s="19" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="19"/>
       <c r="B21" s="19"/>
       <c r="C21" s="19" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19"/>
       <c r="B22" s="19"/>
       <c r="C22" s="19" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="19"/>
       <c r="B23" s="19"/>
       <c r="C23" s="19" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="19"/>
       <c r="B24" s="19" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="19"/>
       <c r="B25" s="19"/>
       <c r="C25" s="19" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19"/>
       <c r="B26" s="19" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="19"/>
       <c r="B27" s="19"/>
       <c r="C27" s="19" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="19"/>
       <c r="B29" s="19"/>
       <c r="C29" s="19" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F29" s="19"/>
     </row>
@@ -2306,13 +2210,13 @@
       <c r="A30" s="19"/>
       <c r="B30" s="19"/>
       <c r="C30" s="19" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F30" s="19"/>
     </row>
@@ -2320,29 +2224,29 @@
       <c r="A31" s="19"/>
       <c r="B31" s="19"/>
       <c r="C31" s="19" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F31" s="19"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="19"/>
       <c r="B32" s="19" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F32" s="19"/>
     </row>
@@ -2350,13 +2254,13 @@
       <c r="A33" s="19"/>
       <c r="B33" s="19"/>
       <c r="C33" s="19" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F33" s="19"/>
     </row>
@@ -2364,95 +2268,95 @@
       <c r="A34" s="19"/>
       <c r="B34" s="19"/>
       <c r="C34" s="19" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F34" s="19"/>
     </row>
     <row r="35" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="19"/>
       <c r="B35" s="19" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="19"/>
       <c r="B36" s="19"/>
       <c r="C36" s="19" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="19"/>
       <c r="B37" s="19" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="18" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="19"/>
       <c r="B39" s="19"/>
       <c r="C39" s="19" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F39" s="19"/>
     </row>
@@ -2460,13 +2364,13 @@
       <c r="A40" s="19"/>
       <c r="B40" s="19"/>
       <c r="C40" s="19" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F40" s="19"/>
     </row>
@@ -2474,13 +2378,13 @@
       <c r="A41" s="19"/>
       <c r="B41" s="19"/>
       <c r="C41" s="19" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F41" s="19"/>
     </row>
@@ -2488,29 +2392,29 @@
       <c r="A42" s="19"/>
       <c r="B42" s="19"/>
       <c r="C42" s="19" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F42" s="19"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="19"/>
       <c r="B43" s="19" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F43" s="19"/>
     </row>
@@ -2518,13 +2422,13 @@
       <c r="A44" s="19"/>
       <c r="B44" s="19"/>
       <c r="C44" s="19" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F44" s="19"/>
     </row>
@@ -2532,47 +2436,47 @@
       <c r="A45" s="19"/>
       <c r="B45" s="19"/>
       <c r="C45" s="19" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F45" s="19"/>
     </row>
     <row r="46" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="19"/>
       <c r="B46" s="19" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="19"/>
       <c r="B47" s="19" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F47" s="19"/>
     </row>
@@ -2592,7 +2496,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:J19"/>
+  <dimension ref="A2:J34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21"/>
@@ -2608,58 +2512,58 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2673,7 +2577,7 @@
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">F6-E6-D6-B6-A6</f>
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D6" s="22" t="n">
         <f aca="false">COUNTIF(F9:F996,"Blocked")</f>
@@ -2685,53 +2589,53 @@
       </c>
       <c r="F6" s="22" t="n">
         <f aca="false">COUNTA(A9:A996)</f>
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="23"/>
@@ -2739,19 +2643,19 @@
     </row>
     <row r="10" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="23"/>
@@ -2759,19 +2663,19 @@
     </row>
     <row r="11" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="23"/>
@@ -2779,19 +2683,19 @@
     </row>
     <row r="12" customFormat="false" ht="121.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="23"/>
@@ -2799,19 +2703,19 @@
     </row>
     <row r="13" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="23"/>
@@ -2819,19 +2723,19 @@
     </row>
     <row r="14" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="23"/>
@@ -2839,19 +2743,19 @@
     </row>
     <row r="15" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="23"/>
@@ -2859,19 +2763,19 @@
     </row>
     <row r="16" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="23"/>
@@ -2879,19 +2783,19 @@
     </row>
     <row r="17" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="23"/>
@@ -2899,19 +2803,19 @@
     </row>
     <row r="18" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="23"/>
@@ -2919,23 +2823,321 @@
     </row>
     <row r="19" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="23"/>
       <c r="H19" s="9"/>
+    </row>
+    <row r="20" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="9"/>
+    </row>
+    <row r="21" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="9"/>
+    </row>
+    <row r="22" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="9"/>
+    </row>
+    <row r="23" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="9"/>
+    </row>
+    <row r="24" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" s="8"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="9"/>
+    </row>
+    <row r="25" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" s="8"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="9"/>
+    </row>
+    <row r="26" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="8"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="9"/>
+    </row>
+    <row r="27" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" s="8"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="9"/>
+    </row>
+    <row r="28" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="8"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="9"/>
+    </row>
+    <row r="29" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="9"/>
+    </row>
+    <row r="30" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F30" s="8"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="9"/>
+    </row>
+    <row r="31" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="8"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="9"/>
+    </row>
+    <row r="32" customFormat="false" ht="121.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" s="8"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="9"/>
+    </row>
+    <row r="33" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F33" s="8"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="9"/>
+    </row>
+    <row r="34" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F34" s="8"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F9:F996">
@@ -2970,778 +3172,6 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:J19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J4" s="21" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="n">
-        <f aca="false">COUNTIF(F9:F996,"Passed")</f>
-        <v>0</v>
-      </c>
-      <c r="B6" s="22" t="n">
-        <f aca="false">COUNTIF(F9:F996,"Failed")</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <f aca="false">F6-E6-D6-B6-A6</f>
-        <v>11</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <f aca="false">COUNTIF(F9:F996,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="22" t="n">
-        <f aca="false">COUNTIF(F9:F996,"Skipped")</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <f aca="false">COUNTA(A9:A996)</f>
-        <v>11</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="9"/>
-    </row>
-    <row r="15" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="9"/>
-    </row>
-    <row r="16" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="9"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F9:F996">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>"Passed"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>"Blocked"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F9:F996" type="list">
-      <formula1>$J$2:$J$6</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A2:J10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J4" s="21" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="n">
-        <f aca="false">COUNTIF(F9:F996,"Passed")</f>
-        <v>0</v>
-      </c>
-      <c r="B6" s="22" t="n">
-        <f aca="false">COUNTIF(F9:F996,"Failed")</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <f aca="false">F6-E6-D6-B6-A6</f>
-        <v>2</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <f aca="false">COUNTIF(F9:F996,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="22" t="n">
-        <f aca="false">COUNTIF(F9:F996,"Skipped")</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <f aca="false">COUNTA(A9:A996)</f>
-        <v>2</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="121.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="9"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F9:F996">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>"Passed"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>"Blocked"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F9:F996" type="list">
-      <formula1>$J$2:$J$6</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A2:J10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J4" s="21" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="n">
-        <f aca="false">COUNTIF(F9:F996,"Passed")</f>
-        <v>0</v>
-      </c>
-      <c r="B6" s="22" t="n">
-        <f aca="false">COUNTIF(F9:F996,"Failed")</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <f aca="false">F6-E6-D6-B6-A6</f>
-        <v>2</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <f aca="false">COUNTIF(F9:F996,"Blocked")</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="22" t="n">
-        <f aca="false">COUNTIF(F9:F996,"Skipped")</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <f aca="false">COUNTA(A9:A996)</f>
-        <v>2</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="9"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F9:F996">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>"Passed"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>"Failed"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>"Blocked"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F9:F996" type="list">
-      <formula1>$J$2:$J$6</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
   <dimension ref="B1:I18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -3754,7 +3184,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="11" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3789,7 +3219,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>9</v>
@@ -3800,7 +3230,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="2" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3808,25 +3238,25 @@
         <v>27</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3834,136 +3264,37 @@
         <v>1</v>
       </c>
       <c r="C11" s="9" t="str">
-        <f aca="false">'Add Contract'!B2</f>
-        <v>ADD_CONTRACT</v>
+        <f aca="false">Contracts!B2</f>
+        <v>CONTRACT</v>
       </c>
       <c r="D11" s="8" t="n">
-        <f aca="false">'Add Contract'!A6</f>
+        <f aca="false">Contracts!A6</f>
         <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
-        <f aca="false">'Add Contract'!B6</f>
+        <f aca="false">Contracts!B6</f>
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <f aca="false">'Add Contract'!C6</f>
-        <v>11</v>
+        <f aca="false">Contracts!C6</f>
+        <v>26</v>
       </c>
       <c r="G11" s="8" t="n">
-        <f aca="false">'Add Contract'!D6</f>
+        <f aca="false">Contracts!D6</f>
         <v>0</v>
       </c>
       <c r="H11" s="8" t="n">
-        <f aca="false">'Add Contract'!E6</f>
+        <f aca="false">Contracts!E6</f>
         <v>0</v>
       </c>
       <c r="I11" s="8" t="n">
-        <f aca="false">'Add Contract'!F6</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="9" t="str">
-        <f aca="false">'List Contract'!B2</f>
-        <v>LIST_CONTRACT</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <f aca="false">'List Contract'!A6</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <f aca="false">'List Contract'!B6</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <f aca="false">'List Contract'!C6</f>
-        <v>11</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <f aca="false">'List Contract'!D6</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <f aca="false">'List Contract'!E6</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <f aca="false">'List Contract'!F6</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="9" t="str">
-        <f aca="false">'Edit Contract'!B2</f>
-        <v>EDIT_CONTRACT</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <f aca="false">'Edit Contract'!A6</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <f aca="false">'Edit Contract'!B6</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <f aca="false">'Edit Contract'!C6</f>
-        <v>2</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <f aca="false">'Edit Contract'!D6</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <f aca="false">'Edit Contract'!E6</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <f aca="false">'Edit Contract'!F6</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C14" s="9" t="str">
-        <f aca="false">'Delete Contract'!B2</f>
-        <v>DELETE_CONTRACT</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <f aca="false">'Delete Contract'!A6</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <f aca="false">'Delete Contract'!B6</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <f aca="false">'Delete Contract'!C6</f>
-        <v>2</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <f aca="false">'Delete Contract'!D6</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <f aca="false">'Delete Contract'!E6</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <f aca="false">'Delete Contract'!F6</f>
-        <v>2</v>
+        <f aca="false">Contracts!F6</f>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="7" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="D15" s="7" t="n">
         <f aca="false">SUM(D11:D14)</f>
@@ -3992,26 +3323,26 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="2" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="E17" s="24" t="n">
         <f aca="false">IFERROR((D15+E15)*100/(I15-G15-H15),0)</f>
         <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="2" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="E18" s="24" t="n">
         <f aca="false">IFERROR(D15*100/(D15+E15),0)</f>
         <v>0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
